--- a/docs/Test_Report/Port/TestPlanExecutionReport.xlsx
+++ b/docs/Test_Report/Port/TestPlanExecutionReport.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000,MCAL-27001</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21 03:49:22.722043-05:00 CDT</t>
+          <t>2024-12-18 07:05:52.651350-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="7" t="inlineStr">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1537,12 +1537,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1668,12 +1668,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1799,12 +1799,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1930,12 +1930,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2061,12 +2061,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2193,12 +2193,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2324,12 +2324,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2455,12 +2455,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2586,12 +2586,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2717,12 +2717,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2851,12 +2851,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2985,12 +2985,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3119,12 +3119,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3253,12 +3253,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3385,12 +3385,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3519,12 +3519,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3650,12 +3650,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3781,12 +3781,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3916,12 +3916,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4050,12 +4050,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4185,12 +4185,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4319,12 +4319,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4450,12 +4450,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4581,12 +4581,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4712,12 +4712,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4843,12 +4843,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4974,12 +4974,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5105,12 +5105,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5237,12 +5237,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5369,12 +5369,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5503,12 +5503,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5634,12 +5634,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5765,12 +5765,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5896,12 +5896,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6030,12 +6030,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6161,12 +6161,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26998</t>
+          <t>MCAL-28002</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85x - MCAL PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27000</t>
+          <t>MCAL-28003</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6289,1400 +6289,8 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26402</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Validate Static configuration provided to Port Driver to initialize port</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21439</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>Validate Static configuration provided to Port Driver to initialize port</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Port driver should allow static configuration as input to initialize Port driver
-</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26401</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Validate Static configuration of Port Pin names provided to Port Driver</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21440</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Validate Static configuration of Port Pin names provided to Port Driver</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Port driver should allow static configuration of Port pin names
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="inlineStr"/>
-      <c r="U39" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26400</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Port Driver service to Set the direction of Port pins</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21441</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Port Driver service to Set the direction of Port pins</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>Port driver should Set the directions of the pins</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr"/>
-      <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26395</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test to verify Autosar and design specific datatypes and MACRO</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22331,MCAL-22336,MCAL-22391,MCAL-22393,MCAL-22398,MCAL-22405,MCAL-23518,MCAL-23519,MCAL-23520,MCAL-22339,MCAL-23517,MCAL-22392,MCAL-22402,MCAL-22705,MCAL-22330,MCAL-22334,MCAL-22335,MCAL-22337,MCAL-22338,MCAL-22394,MCAL-22396,MCAL-22397,MCAL-22404,MCAL-23522,MCAL-22332,MCAL-22333,MCAL-22403,MCAL-23521,MCAL-23523</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test to verify Autosar and design specific datatypes and MACRO</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>Port Driver should contain all Autosar and design specific datatypes and MACRO</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26386</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual Test to verify Autosar and design specific PORT Containers </t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22380,MCAL-22406,MCAL-22407,MCAL-22414,MCAL-22368,MCAL-23158,MCAL-22370,MCAL-22371,MCAL-22373,MCAL-22377,MCAL-22378,MCAL-22369,MCAL-22366,MCAL-22367,MCAL-22372,MCAL-22374,MCAL-22375,MCAL-22376,MCAL-22381,MCAL-23153,MCAL-23159,MCAL-22379,MCAL-22408,MCAL-22410,MCAL-23154,MCAL-23155,MCAL-23156,MCAL-23157,MCAL-23160</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual Test to verify Autosar and design specific Containers </t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Port Driver should contain all Autosar and design specific Containers </t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25520</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Test to verify All Reentrant functions of Port Driver performing register access in atomic way</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21443</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Test to verify All Reentrant functions of Port Driver performing register access in atomic way</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>Check manually in the driver code whether it handles the reentrant</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25519</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Verify Port and Port pins that are not used are set to a defined state</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21444</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>Verify Port and Port pins that are not used are set to a defined state</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Check manually if non used registers have defined state. Hardware needs to take care
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr"/>
-      <c r="T44" s="3" t="inlineStr"/>
-      <c r="U44" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25518</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Port Driver service to Refresh the direction of Port pins</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21442</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Port Driver service to Refresh the direction of Port pins</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>Port driver should refresh the directions of the pins</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25517</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test to verify inclusions of all header files and file structure for PORT Driver</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Design,Design,Design,Design,Design</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22309,MCAL-22310,MCAL-22308,MCAL-22307,MCAL-22312</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test to verify inclusions of all header files and file structure</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>All header files and file structure are present as per autosar</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25511</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Test to check Port_ConfigType,Port_PinType,Port_PinDirectionType,Port_PinModeType Datatypes in Code</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Architecture,Architecture,Architecture,Architecture</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22296,MCAL-22299,MCAL-22297,MCAL-22298</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Test to check Port_ConfigType,Port_PinType,Port_PinDirectionType,
-Port_PinModeType Datatypes in Code</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>All Datatypes:
-Port_ConfigType,Port_PinType,Port_PinDirectionType,
-Port_PinModeType are present in Code</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr"/>
-      <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25490</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Verify Autosar specified Container Parameters</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22305</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>Verify if Autosar specified Container parameters are present</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manually verified Autosar specified container parameters </t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="inlineStr"/>
-      <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27022</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To verify Port Header File inclusions to satisfy AUTOSAR 4.3.1 requirements</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27020</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify all header files required for Port driver are included correctly as per Autosar 4.3.1 requirements</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>All header files required for Port driver are included correctly as per Autosar 4.3.1 requirements</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R49" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S49" s="3" t="inlineStr"/>
-      <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27032</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To Verify AUTOSAR 4.3.1 BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-12326,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425,MCAL-12447,MCAL-12438,MCAL-12444,MCAL-12357,MCAL-12330</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify all Modules Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>Module Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="inlineStr">
-        <is>
-          <t>Can,Dio,Gpt,Mcu,Port</t>
-        </is>
-      </c>
-      <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S50" s="3" t="inlineStr"/>
-      <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26999</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27033</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To Verify AUTOSAR 4.3.1 Functional requirement</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement,Requirement,Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26907,MCAL-26985,MCAL-22250,MCAL-26908,MCAL-27018</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify AUTOSAR 4.3.1 Functional requirement.</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>AUTOSAR 4.3.1 Requirements are satisfied</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27001</t>
-        </is>
-      </c>
-      <c r="R51" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : PORT - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S51" s="3" t="inlineStr"/>
-      <c r="T51" s="3" t="inlineStr"/>
-      <c r="U51" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U51"/>
+  <autoFilter ref="A1:U37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
